--- a/delivery/planning/safety_eval_data_checklist_20261025.xlsx
+++ b/delivery/planning/safety_eval_data_checklist_20261025.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>K45+500 有（设计洪水位 34.04 m；符合 2 级堤防防洪标准）</t>
+          <t>K45+500 有（设计洪水位 33.89 m；符合 2 级堤防防洪标准）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34.04</t>
+          <t>33.89</t>
         </is>
       </c>
     </row>
